--- a/output/ic_report.xlsx
+++ b/output/ic_report.xlsx
@@ -490,162 +490,162 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>因子</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>n_t1</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>ic_mean_t1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>ic_std_t1</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ic_ir_t1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>t_nw_t1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>p_nw_t1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>win_rate_t1</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ic_boot_lo_t1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ic_boot_hi_t1</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ir_boot_lo_t1</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ir_boot_hi_t1</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>boot_p_positive_t1</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>CI含0_t1</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>方向_t1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>结论_t1</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>n_t2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>ic_mean_t2</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>ic_std_t2</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>ic_ir_t2</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>t_nw_t2</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>p_nw_t2</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>win_rate_t2</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>ic_boot_lo_t2</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ic_boot_hi_t2</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ir_boot_lo_t2</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>ir_boot_hi_t2</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>boot_p_positive_t2</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>CI含0_t2</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>方向_t2</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>结论_t2</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>IC方向一致(t1/t2)</t>
         </is>
@@ -658,17 +658,21 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5296244104353879</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+        <v>0.04067173893361262</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.6914834993963672</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.05881809033638134</v>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
@@ -687,14 +691,18 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-0.6503163002128891</v>
+      </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
@@ -708,7 +716,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>样本不足</t>
+          <t>边际可用</t>
         </is>
       </c>
       <c r="AF2" t="b">
@@ -722,101 +730,101 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.07310483870967745</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.2874919284584838</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.2542848388880399</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.049643414407494</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.3212493306059305</v>
+      </c>
+      <c r="H3" t="n">
+        <v>70</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-0.09255846774193549</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.2280241935483872</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-0.2738022367006415</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.453947450724719</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.821</v>
+      </c>
+      <c r="N3" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>拥挤=风险(期望负)</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>边际可用</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
         <v>9</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.1405017921146954</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.204650018572552</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.6865466863609643</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2.187061496541545</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.06019613646604394</v>
-      </c>
-      <c r="H3" t="n">
-        <v>77.77777777777779</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.0388888888888889</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.2494332437275986</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.1805737191472907</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.666414883604412</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="R3" t="n">
+        <v>0.04130824372759857</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.2708110949673537</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.1525352708779464</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.5494354843932925</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.5977051846010397</v>
+      </c>
+      <c r="W3" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.1351702508960574</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.1946236559139785</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-0.4885604763914538</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.646087911767393</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="AC3" t="b">
         <v>1</v>
       </c>
-      <c r="N3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>拥挤=风险(期望负)</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>优秀(方向相反)</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>8</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.1110383064516129</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.183857442694721</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.6039369678168656</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.589358708426592</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.156003793405799</v>
-      </c>
-      <c r="W3" t="n">
-        <v>75</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.02394153225806452</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.1981350806451613</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0.1286233382427749</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.619194223154589</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0.985</v>
-      </c>
-      <c r="AC3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>拥挤=风险(期望负)</t>
-        </is>
-      </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>优秀(方向相反)</t>
+          <t>边际可用</t>
         </is>
       </c>
       <c r="AF3" t="b">
@@ -830,101 +838,101 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.07310483870967745</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.2874919284584838</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.2542848388880399</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.049643414407494</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.3212493306059305</v>
+      </c>
+      <c r="H4" t="n">
+        <v>70</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0.09255846774193549</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.2280241935483872</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.2738022367006415</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.453947450724719</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.821</v>
+      </c>
+      <c r="N4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>拥挤=风险(期望负)</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>边际可用</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
         <v>9</v>
       </c>
-      <c r="C4" t="n">
-        <v>0.1405017921146954</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.204650018572552</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.6865466863609643</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2.187061496541545</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.06019613646604394</v>
-      </c>
-      <c r="H4" t="n">
-        <v>77.77777777777779</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.0388888888888889</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.2494332437275986</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.1805737191472907</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.666414883604412</v>
-      </c>
-      <c r="M4" t="n">
+      <c r="R4" t="n">
+        <v>0.04130824372759857</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.2708110949673537</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.1525352708779464</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.5494354843932925</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.5977051846010397</v>
+      </c>
+      <c r="W4" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-0.1351702508960574</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.1946236559139785</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-0.4885604763914538</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.646087911767393</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="AC4" t="b">
         <v>1</v>
       </c>
-      <c r="N4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>拥挤=风险(期望负)</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>优秀(方向相反)</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>8</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.1110383064516129</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.183857442694721</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.6039369678168656</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.589358708426592</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.156003793405799</v>
-      </c>
-      <c r="W4" t="n">
-        <v>75</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.02394153225806452</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.1981350806451613</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0.1286233382427749</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.619194223154589</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0.985</v>
-      </c>
-      <c r="AC4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>拥挤=风险(期望负)</t>
-        </is>
-      </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>优秀(方向相反)</t>
+          <t>边际可用</t>
         </is>
       </c>
       <c r="AF4" t="b">
@@ -938,101 +946,101 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.0908467741935484</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2764847379862867</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.328577898567603</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.374308015178582</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2025965100482681</v>
+      </c>
+      <c r="H5" t="n">
+        <v>70</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.05828225806451614</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.2399526209677419</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0.2136073194769981</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.515374160111946</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="N5" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>拥挤=风险(期望负)</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>有效(方向相反)</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
         <v>9</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.1487903225806452</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.2196085611611619</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.6775251465331261</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2.161600329998009</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.06263302086838274</v>
-      </c>
-      <c r="H5" t="n">
-        <v>77.77777777777779</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.0335483870967742</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.2692618727598566</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.1649435425685969</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.939197651757481</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.997</v>
-      </c>
-      <c r="N5" t="b">
-        <v>0</v>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="R5" t="n">
+        <v>0.03897849462365593</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.2851572734308748</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.1366912165861508</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.4888850542104487</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.6380433201537399</v>
+      </c>
+      <c r="W5" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.1526030465949821</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.2056451612903226</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-0.5389782288563373</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.697504168716551</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="AC5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD5" t="inlineStr">
         <is>
           <t>拥挤=风险(期望负)</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>优秀(方向相反)</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>8</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.1102822580645162</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.20158409932492</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.5470781596060288</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.400800302086983</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.2040115893134831</v>
-      </c>
-      <c r="W5" t="n">
-        <v>75</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.01219758064516129</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.208366935483871</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0.05850640921791687</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.656773440915555</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0.985</v>
-      </c>
-      <c r="AC5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>拥挤=风险(期望负)</t>
-        </is>
-      </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>优秀(方向相反)</t>
+          <t>边际可用</t>
         </is>
       </c>
       <c r="AF5" t="b">
@@ -1046,40 +1054,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>0.09231891990512681</v>
+        <v>0.03430070312828935</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2112691109122604</v>
+        <v>0.2708068829795762</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4369731074575623</v>
+        <v>0.1266611200974395</v>
       </c>
       <c r="F6" t="n">
-        <v>1.445023771325356</v>
+        <v>0.4346714330390894</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1864554326706946</v>
+        <v>0.6740366668278759</v>
       </c>
       <c r="H6" t="n">
-        <v>66.66666666666666</v>
+        <v>60</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.02152435686918442</v>
+        <v>-0.1378623594796008</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2034330718238763</v>
+        <v>0.1867036124794746</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.09528045401288782</v>
+        <v>-0.4475252459924766</v>
       </c>
       <c r="L6" t="n">
-        <v>3.145090778954919</v>
+        <v>2.01686169582638</v>
       </c>
       <c r="M6" t="n">
-        <v>0.929</v>
+        <v>0.662</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -1091,56 +1099,56 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>边际可用</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>9</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.06625919844310649</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.2089113422506208</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.317164198598746</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.004780518969402</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.3444225421159941</v>
+      </c>
+      <c r="W6" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.05871799549960471</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.1755982789028765</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-0.2765390002728871</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.100179058628219</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AC6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>拥挤=风险(期望负)</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
           <t>有效(方向相反)</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>8</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.122092227695676</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.1334723278812782</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.9147381306204185</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3.028971330474218</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.01914235969634226</v>
-      </c>
-      <c r="W6" t="n">
-        <v>75</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.0668103448275862</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.1773741105637657</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0.4448820033496298</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.949975892873494</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>拥挤=风险(期望负)</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>优秀(方向相反)</t>
         </is>
       </c>
       <c r="AF6" t="b">
@@ -1154,37 +1162,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.1391452991452991</v>
+        <v>-0.174017094017094</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2367222049023127</v>
+        <v>0.2489406456104991</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5877999455214593</v>
+        <v>-0.6990304600132154</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.701734962320742</v>
+        <v>-3.085491527868635</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02700139673357338</v>
+        <v>0.01302393837169813</v>
       </c>
       <c r="H7" t="n">
-        <v>33.33333333333333</v>
+        <v>30</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2499145299145299</v>
+        <v>-0.2874393162393162</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.05613295346628683</v>
+        <v>-0.06762393162393163</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.117900217173947</v>
+        <v>-1.334763518031181</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.2599053462246689</v>
+        <v>-0.3192542832410054</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1203,37 +1211,37 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.1446153846153846</v>
+        <v>-0.1499335232668566</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2969874659817698</v>
+        <v>0.2782640903349465</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4869410368458499</v>
+        <v>-0.5388173626226135</v>
       </c>
       <c r="U7" t="n">
-        <v>-2.289325516604351</v>
+        <v>-2.661615686505738</v>
       </c>
       <c r="V7" t="n">
-        <v>0.05586303548574234</v>
+        <v>0.02873338855889895</v>
       </c>
       <c r="W7" t="n">
-        <v>37.5</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1986324786324786</v>
+        <v>-0.2474833808167142</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.0905982905982906</v>
+        <v>-0.07000379867046536</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.8563484923669155</v>
+        <v>-1.2413666590645</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.2676464965327945</v>
+        <v>-0.2313975306299892</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1248,7 +1256,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>有效</t>
+          <t>优秀</t>
         </is>
       </c>
       <c r="AF7" t="b">
@@ -1262,40 +1270,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02400607873892374</v>
+        <v>-0.02388318479012398</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2759825151410172</v>
+        <v>0.3322550803450822</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08698405667713223</v>
+        <v>-0.07188207555869051</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4664405569649532</v>
+        <v>-0.4243048328905329</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6476023690524975</v>
+        <v>0.6769936218410821</v>
       </c>
       <c r="H8" t="n">
-        <v>62.5</v>
+        <v>58.82352941176471</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0512601145676508</v>
+        <v>-0.1498848178990975</v>
       </c>
       <c r="J8" t="n">
-        <v>0.09893471501924581</v>
+        <v>0.08635683816527179</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1737744487681194</v>
+        <v>-0.4210347164981194</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5192203487111642</v>
+        <v>0.384859512872521</v>
       </c>
       <c r="M8" t="n">
-        <v>0.735</v>
+        <v>0.383</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
@@ -1311,40 +1319,40 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.000558832699954596</v>
+        <v>-0.02490892443120567</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2631065911998884</v>
+        <v>0.2722074660764512</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.002123978336711593</v>
+        <v>-0.09150713163837261</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.00850966754924967</v>
+        <v>-0.3784064604903313</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9933304223142587</v>
+        <v>0.7104304976945091</v>
       </c>
       <c r="W8" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1213754979089983</v>
+        <v>-0.1466390517111172</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1181208481269715</v>
+        <v>0.1058476908993773</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.4940841528596449</v>
+        <v>-0.6371399466870674</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.5891157512841473</v>
+        <v>0.4450005543413859</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.518</v>
+        <v>0.362</v>
       </c>
       <c r="AC8" t="b">
         <v>1</v>
@@ -1360,7 +1368,7 @@
         </is>
       </c>
       <c r="AF8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1370,17 +1378,21 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01814516129032258</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+        <v>-0.1522177419354839</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.2409295282671906</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.6317936328944892</v>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
@@ -1395,18 +1407,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>无效</t>
+          <t>优秀</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-0.03750000000000001</v>
+      </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
@@ -1420,11 +1436,11 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>样本不足</t>
+          <t>边际可用</t>
         </is>
       </c>
       <c r="AF9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1434,17 +1450,21 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01814516129032258</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+        <v>-0.1522177419354839</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.2409295282671906</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.6317936328944892</v>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
@@ -1459,18 +1479,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>无效</t>
+          <t>优秀</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-0.03750000000000001</v>
+      </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
@@ -1484,11 +1508,11 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>样本不足</t>
+          <t>边际可用</t>
         </is>
       </c>
       <c r="AF10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1498,37 +1522,37 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.04251152073732718</v>
+        <v>-0.04345105672969966</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2832478373782312</v>
+        <v>0.2781898686331973</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1500859499257535</v>
+        <v>-0.1561920890332327</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.823102482420108</v>
+        <v>-0.8695583190076015</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4176606948172403</v>
+        <v>0.3919352308989912</v>
       </c>
       <c r="H11" t="n">
-        <v>46.42857142857143</v>
+        <v>44.82758620689656</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1474434763824884</v>
+        <v>-0.1414832452725251</v>
       </c>
       <c r="J11" t="n">
-        <v>0.06236316641506433</v>
+        <v>0.06267051992635495</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5413844136603359</v>
+        <v>-0.5641280980196064</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2418535585345141</v>
+        <v>0.2426653133248487</v>
       </c>
       <c r="M11" t="n">
         <v>0.191</v>
@@ -1547,40 +1571,40 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.01723056482511433</v>
+        <v>-0.01353339027490864</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2719770835799345</v>
+        <v>0.2676090101973509</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.06335300238650528</v>
+        <v>-0.05057150454287136</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3757278526568528</v>
+        <v>-0.3066581289898294</v>
       </c>
       <c r="V11" t="n">
-        <v>0.7101674100598876</v>
+        <v>0.761456105195474</v>
       </c>
       <c r="W11" t="n">
-        <v>55.55555555555556</v>
+        <v>57.14285714285714</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1046294751369835</v>
+        <v>-0.09820072898458609</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.07216396562023646</v>
+        <v>0.08027618733116158</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.3825283814893533</v>
+        <v>-0.3582525360095257</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.2870173219289819</v>
+        <v>0.337252881116189</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.311</v>
+        <v>0.343</v>
       </c>
       <c r="AC11" t="b">
         <v>1</v>
@@ -1606,101 +1630,101 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.1302016129032258</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.2599016464686036</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.5009649406701788</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.21331417380362</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.05415164159707953</v>
+      </c>
+      <c r="H12" t="n">
+        <v>70</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.00645161290322579</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.2555241935483871</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.02199977488539966</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.310121198417517</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="N12" t="b">
+        <v>1</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>拥挤=风险(期望负)</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>优秀(方向相反)</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
         <v>9</v>
       </c>
-      <c r="C12" t="n">
-        <v>0.180331541218638</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.2184516303361188</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.8254987199737186</v>
-      </c>
-      <c r="F12" t="n">
-        <v>3.280357006643533</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.01118184788808918</v>
-      </c>
-      <c r="H12" t="n">
+      <c r="R12" t="n">
+        <v>0.118010752688172</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.3128537280021927</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.3772074363369738</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.618235345737517</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.1442727718039922</v>
+      </c>
+      <c r="W12" t="n">
         <v>77.77777777777779</v>
       </c>
-      <c r="I12" t="n">
-        <v>0.1014325716845878</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.2750448028673836</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.4638151016388223</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.466300937141717</v>
-      </c>
-      <c r="M12" t="n">
+      <c r="X12" t="n">
+        <v>-0.01557683691756272</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.2428001792114696</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0.04356871490063458</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.171464321281942</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="AC12" t="b">
         <v>1</v>
       </c>
-      <c r="N12" t="b">
-        <v>0</v>
-      </c>
-      <c r="O12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>拥挤=风险(期望负)</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>优秀(方向相反)</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>8</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.2032258064516129</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.1927930248700178</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.054113895399634</v>
-      </c>
-      <c r="U12" t="n">
-        <v>5.867845721750649</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0.0006192907498556721</v>
-      </c>
-      <c r="W12" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0.147983870967742</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0.2584677419354839</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0.7626497674585043</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.620425220187451</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>拥挤=风险(期望负)</t>
-        </is>
-      </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>优秀(方向相反)</t>
+          <t>有效(方向相反)</t>
         </is>
       </c>
       <c r="AF12" t="b">
@@ -1714,101 +1738,101 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.1302016129032258</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.2599016464686036</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.5009649406701788</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.21331417380362</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.05415164159707953</v>
+      </c>
+      <c r="H13" t="n">
+        <v>70</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0.00645161290322579</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.2555241935483871</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.02199977488539966</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.310121198417517</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="N13" t="b">
+        <v>1</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>拥挤=风险(期望负)</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>优秀(方向相反)</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
         <v>9</v>
       </c>
-      <c r="C13" t="n">
-        <v>0.180331541218638</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.2184516303361188</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.8254987199737186</v>
-      </c>
-      <c r="F13" t="n">
-        <v>3.280357006643533</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.01118184788808918</v>
-      </c>
-      <c r="H13" t="n">
+      <c r="R13" t="n">
+        <v>0.118010752688172</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.3128537280021927</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.3772074363369738</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.618235345737517</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.1442727718039922</v>
+      </c>
+      <c r="W13" t="n">
         <v>77.77777777777779</v>
       </c>
-      <c r="I13" t="n">
-        <v>0.1014325716845878</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.2750448028673836</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.4638151016388223</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.466300937141717</v>
-      </c>
-      <c r="M13" t="n">
+      <c r="X13" t="n">
+        <v>-0.01557683691756272</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.2428001792114696</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0.04356871490063458</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.171464321281942</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="AC13" t="b">
         <v>1</v>
       </c>
-      <c r="N13" t="b">
-        <v>0</v>
-      </c>
-      <c r="O13" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>拥挤=风险(期望负)</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>优秀(方向相反)</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>8</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.2032258064516129</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.1927930248700178</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.054113895399634</v>
-      </c>
-      <c r="U13" t="n">
-        <v>5.867845721750649</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0.0006192907498556721</v>
-      </c>
-      <c r="W13" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.147983870967742</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.2584677419354839</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0.7626497674585043</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.620425220187451</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>拥挤=风险(期望负)</t>
-        </is>
-      </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>优秀(方向相反)</t>
+          <t>有效(方向相反)</t>
         </is>
       </c>
       <c r="AF13" t="b">
@@ -1822,13 +1846,17 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2229838709677419</v>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+        <v>0.1193548387096774</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.1465535828749538</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8144109230786695</v>
+      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
@@ -1847,18 +1875,22 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>边际可用</t>
+          <t>优秀(方向相反)</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-0.2278225806451613</v>
+      </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
@@ -1872,7 +1904,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>样本不足</t>
+          <t>边际可用</t>
         </is>
       </c>
       <c r="AF14" t="b">
@@ -1886,13 +1918,17 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2229838709677419</v>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+        <v>0.1193548387096774</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.1465535828749538</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8144109230786695</v>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
@@ -1911,18 +1947,22 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>边际可用</t>
+          <t>优秀</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-0.2278225806451613</v>
+      </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
@@ -1936,7 +1976,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>样本不足</t>
+          <t>边际可用</t>
         </is>
       </c>
       <c r="AF15" t="b">
@@ -1950,40 +1990,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C16" t="n">
-        <v>0.08050860082631495</v>
+        <v>0.07098883817268228</v>
       </c>
       <c r="D16" t="n">
-        <v>0.25347529320523</v>
+        <v>0.2541323312852173</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3176191249579894</v>
+        <v>0.2793380826975936</v>
       </c>
       <c r="F16" t="n">
-        <v>1.925951351418077</v>
+        <v>1.818107413392554</v>
       </c>
       <c r="G16" t="n">
-        <v>0.06470056745793373</v>
+        <v>0.0797620553077627</v>
       </c>
       <c r="H16" t="n">
-        <v>71.42857142857143</v>
+        <v>68.96551724137932</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0009402560384554277</v>
+        <v>-0.004096853304437888</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1599899814277769</v>
+        <v>0.1492511435119481</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.00379078133532422</v>
+        <v>-0.01632984363592875</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7295507077321735</v>
+        <v>0.6403498811633757</v>
       </c>
       <c r="M16" t="n">
-        <v>0.973</v>
+        <v>0.967</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -1995,44 +2035,44 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>有效</t>
+          <t>边际可用</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R16" t="n">
-        <v>0.031557182878095</v>
+        <v>0.01343705307484506</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2413733845478727</v>
+        <v>0.2555323595265068</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1307401101294005</v>
+        <v>0.05258454584673146</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7941713447448117</v>
+        <v>0.3539990168011441</v>
       </c>
       <c r="V16" t="n">
-        <v>0.4342849044596329</v>
+        <v>0.7260892208205951</v>
       </c>
       <c r="W16" t="n">
-        <v>62.96296296296296</v>
+        <v>60.71428571428571</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.04472835043051952</v>
+        <v>-0.05955545844589227</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.1029000715815927</v>
+        <v>0.09367432067376451</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.1897140574191006</v>
+        <v>-0.2429106639796996</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.4912911200227656</v>
+        <v>0.4263173202448994</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.662</v>
       </c>
       <c r="AC16" t="b">
         <v>1</v>
@@ -2044,7 +2084,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>边际可用</t>
+          <t>无效</t>
         </is>
       </c>
       <c r="AF16" t="b">
@@ -2058,37 +2098,37 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1493794837383471</v>
+        <v>0.1199208512951687</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1543996606819806</v>
+        <v>0.1693211373254163</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9674858291691869</v>
+        <v>0.708245014115953</v>
       </c>
       <c r="F17" t="n">
-        <v>3.360438706804024</v>
+        <v>2.9755834137494</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01207707800926872</v>
+        <v>0.01771945319712631</v>
       </c>
       <c r="H17" t="n">
-        <v>87.5</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="I17" t="n">
-        <v>0.06826419777071452</v>
+        <v>0.0559483038183658</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2304947697059797</v>
+        <v>0.1920233277108421</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4326609678030634</v>
+        <v>0.3262949241257379</v>
       </c>
       <c r="L17" t="n">
-        <v>2.619012364458285</v>
+        <v>1.3752046573763</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
@@ -2107,40 +2147,40 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R17" t="n">
-        <v>0.05438853911582787</v>
+        <v>0.0202695815027197</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1672824004752707</v>
+        <v>0.1824790367977715</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3251300732252949</v>
+        <v>0.1110789593063395</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7383464069245458</v>
+        <v>0.3443867507808253</v>
       </c>
       <c r="V17" t="n">
-        <v>0.4881670338324535</v>
+        <v>0.7406699183613679</v>
       </c>
       <c r="W17" t="n">
-        <v>71.42857142857143</v>
+        <v>62.5</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.03572746670184657</v>
+        <v>-0.0838855528635512</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.1445045449335023</v>
+        <v>0.1244247158689906</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0.3046523227775817</v>
+        <v>-0.6611501898629843</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.494757541592109</v>
+        <v>1.42925952587644</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.877</v>
+        <v>0.602</v>
       </c>
       <c r="AC17" t="b">
         <v>1</v>
@@ -2152,7 +2192,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>有效(方向相反)</t>
+          <t>无效</t>
         </is>
       </c>
       <c r="AF17" t="b">
@@ -2166,37 +2206,37 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1493794837383471</v>
+        <v>0.1199208512951687</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1543996606819806</v>
+        <v>0.1693211373254163</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9674858291691869</v>
+        <v>0.708245014115953</v>
       </c>
       <c r="F18" t="n">
-        <v>3.360438706804024</v>
+        <v>2.9755834137494</v>
       </c>
       <c r="G18" t="n">
-        <v>0.01207707800926872</v>
+        <v>0.01771945319712631</v>
       </c>
       <c r="H18" t="n">
-        <v>87.5</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="I18" t="n">
-        <v>0.06826419777071452</v>
+        <v>0.0559483038183658</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2304947697059797</v>
+        <v>0.1920233277108421</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4326609678030634</v>
+        <v>0.3262949241257379</v>
       </c>
       <c r="L18" t="n">
-        <v>2.619012364458285</v>
+        <v>1.3752046573763</v>
       </c>
       <c r="M18" t="n">
         <v>1</v>
@@ -2215,40 +2255,40 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R18" t="n">
-        <v>0.05438853911582787</v>
+        <v>0.0202695815027197</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1672824004752707</v>
+        <v>0.1824790367977715</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3251300732252949</v>
+        <v>0.1110789593063395</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7383464069245458</v>
+        <v>0.3443867507808253</v>
       </c>
       <c r="V18" t="n">
-        <v>0.4881670338324535</v>
+        <v>0.7406699183613679</v>
       </c>
       <c r="W18" t="n">
-        <v>71.42857142857143</v>
+        <v>62.5</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.03572746670184657</v>
+        <v>-0.0838855528635512</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.1445045449335023</v>
+        <v>0.1244247158689906</v>
       </c>
       <c r="Z18" t="n">
-        <v>-0.3046523227775817</v>
+        <v>-0.6611501898629843</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.494757541592109</v>
+        <v>1.42925952587644</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.877</v>
+        <v>0.602</v>
       </c>
       <c r="AC18" t="b">
         <v>1</v>
@@ -2260,7 +2300,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>有效</t>
+          <t>无效</t>
         </is>
       </c>
       <c r="AF18" t="b">
@@ -2274,40 +2314,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0866641177397932</v>
+        <v>0.0783885492271435</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2523521547555121</v>
+        <v>0.2526240004833397</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3434253130263798</v>
+        <v>0.3102973156832466</v>
       </c>
       <c r="F19" t="n">
-        <v>2.131159325878816</v>
+        <v>2.042762720377586</v>
       </c>
       <c r="G19" t="n">
-        <v>0.04138558809749981</v>
+        <v>0.04965802342479453</v>
       </c>
       <c r="H19" t="n">
-        <v>64.51612903225806</v>
+        <v>62.5</v>
       </c>
       <c r="I19" t="n">
-        <v>0.006995049167927762</v>
+        <v>0.006243081720114019</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1699877598879914</v>
+        <v>0.1558736266013053</v>
       </c>
       <c r="K19" t="n">
-        <v>0.02340260119363134</v>
+        <v>0.02230346440021423</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8017625339261373</v>
+        <v>0.7287056510453543</v>
       </c>
       <c r="M19" t="n">
-        <v>0.978</v>
+        <v>0.982</v>
       </c>
       <c r="N19" t="b">
         <v>0</v>
@@ -2323,40 +2363,40 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R19" t="n">
-        <v>0.0317735651992009</v>
+        <v>0.01578861790483198</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2258860445117483</v>
+        <v>0.2392587783309968</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1406619221115643</v>
+        <v>0.06598971212245178</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9650005331222171</v>
+        <v>0.4961321989722676</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3425233391074927</v>
+        <v>0.6234167167576472</v>
       </c>
       <c r="W19" t="n">
-        <v>60</v>
+        <v>58.06451612903226</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.02934060260348757</v>
+        <v>-0.04332062229273635</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.0899785649277041</v>
+        <v>0.07815320455367056</v>
       </c>
       <c r="Z19" t="n">
-        <v>-0.1361796449695141</v>
+        <v>-0.1836355002629513</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.4247822695774823</v>
+        <v>0.379166308593795</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.843</v>
+        <v>0.707</v>
       </c>
       <c r="AC19" t="b">
         <v>1</v>
@@ -2368,7 +2408,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>边际可用</t>
+          <t>无效</t>
         </is>
       </c>
       <c r="AF19" t="b">
@@ -2382,37 +2422,37 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1603326612903226</v>
+        <v>0.141173835125448</v>
       </c>
       <c r="D20" t="n">
-        <v>0.08874238439259992</v>
+        <v>0.1009670986973796</v>
       </c>
       <c r="E20" t="n">
-        <v>1.806720231687762</v>
+        <v>1.398216220400436</v>
       </c>
       <c r="F20" t="n">
-        <v>6.894535210699196</v>
+        <v>5.826960658775937</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0002324680383045674</v>
+        <v>0.000392918888825422</v>
       </c>
       <c r="H20" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1288306451612903</v>
+        <v>0.1088709677419355</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1918346774193549</v>
+        <v>0.1820575716845878</v>
       </c>
       <c r="K20" t="n">
-        <v>1.42869339136516</v>
+        <v>0.968961304114079</v>
       </c>
       <c r="L20" t="n">
-        <v>2.511186998424997</v>
+        <v>2.379248165381293</v>
       </c>
       <c r="M20" t="n">
         <v>1</v>
@@ -2431,40 +2471,40 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R20" t="n">
-        <v>0.109447004608295</v>
+        <v>0.09611895161290325</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2330786840792236</v>
+        <v>0.2190569755125369</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4695710594071051</v>
+        <v>0.4387851671374978</v>
       </c>
       <c r="U20" t="n">
-        <v>1.189003929573296</v>
+        <v>1.201374595201446</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2793563170972728</v>
+        <v>0.2686715121438428</v>
       </c>
       <c r="W20" t="n">
-        <v>71.42857142857143</v>
+        <v>75</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.03473502304147465</v>
+        <v>-0.0418850806451613</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.2536290322580646</v>
+        <v>0.2341229838709678</v>
       </c>
       <c r="Z20" t="n">
-        <v>-0.2221494309637301</v>
+        <v>-0.3054862283202411</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.880682290778708</v>
+        <v>1.45157574535573</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.909</v>
+        <v>0.857</v>
       </c>
       <c r="AC20" t="b">
         <v>1</v>
@@ -2490,14 +2530,18 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.1024193548387097</v>
+      </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>100</v>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -2511,7 +2555,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>样本不足</t>
+          <t>边际可用</t>
         </is>
       </c>
       <c r="Q21" t="n">
@@ -2550,40 +2594,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C22" t="n">
-        <v>0.07001529477196887</v>
+        <v>0.07266629588431592</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2322311778447439</v>
+        <v>0.2277276373297727</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3014896424405899</v>
+        <v>0.3190930039777639</v>
       </c>
       <c r="F22" t="n">
-        <v>1.425463014423361</v>
+        <v>1.537143825968966</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1674543686294845</v>
+        <v>0.1373385765122557</v>
       </c>
       <c r="H22" t="n">
-        <v>54.16666666666666</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.01480305084352985</v>
+        <v>-0.01843620689655171</v>
       </c>
       <c r="J22" t="n">
-        <v>0.164100910734149</v>
+        <v>0.153948553948832</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.08631464265561863</v>
+        <v>-0.09920934081785079</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7375070642777519</v>
+        <v>0.6981788381597591</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
@@ -2599,40 +2643,40 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R22" t="n">
-        <v>0.01193657203656236</v>
+        <v>0.01355615035224323</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1903036256059811</v>
+        <v>0.1862896590909804</v>
       </c>
       <c r="T22" t="n">
-        <v>0.06272382882119511</v>
+        <v>0.07276920478781197</v>
       </c>
       <c r="U22" t="n">
-        <v>0.280976523886279</v>
+        <v>0.3281951212915695</v>
       </c>
       <c r="V22" t="n">
-        <v>0.78135399122845</v>
+        <v>0.7457332669784975</v>
       </c>
       <c r="W22" t="n">
-        <v>39.1304347826087</v>
+        <v>41.66666666666667</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.0757580886975867</v>
+        <v>-0.06875640178902485</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.1019329145910916</v>
+        <v>0.1001366390897293</v>
       </c>
       <c r="Z22" t="n">
-        <v>-0.5787193798863177</v>
+        <v>-0.4961195749563423</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.4904282994607965</v>
+        <v>0.5157557018611096</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.607</v>
+        <v>0.628</v>
       </c>
       <c r="AC22" t="b">
         <v>1</v>
@@ -2658,40 +2702,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C23" t="n">
-        <v>0.02788461538461539</v>
+        <v>-0.01442972350230415</v>
       </c>
       <c r="D23" t="n">
-        <v>0.326048141341118</v>
+        <v>0.3509942232478301</v>
       </c>
       <c r="E23" t="n">
-        <v>0.08552300059101381</v>
+        <v>-0.04111099997254258</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3589700720012644</v>
+        <v>-0.2142627468194</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7258541882415046</v>
+        <v>0.8336663817849859</v>
       </c>
       <c r="H23" t="n">
-        <v>61.53846153846154</v>
+        <v>57.14285714285714</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1051721464019851</v>
+        <v>-0.1148343894009216</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2050504032258064</v>
+        <v>0.1156782834101383</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3462380770513263</v>
+        <v>-0.3573357703472653</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7423206204951579</v>
+        <v>0.3166744777340365</v>
       </c>
       <c r="M23" t="n">
-        <v>0.634</v>
+        <v>0.4</v>
       </c>
       <c r="N23" t="b">
         <v>1</v>
@@ -2707,40 +2751,40 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R23" t="n">
-        <v>0.08259408602150541</v>
+        <v>0.03756203473945412</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2661211916407734</v>
+        <v>0.302127944103676</v>
       </c>
       <c r="T23" t="n">
-        <v>0.310362679169857</v>
+        <v>0.1243249274769652</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7918993825445521</v>
+        <v>0.385909359113846</v>
       </c>
       <c r="V23" t="n">
-        <v>0.4451609892191879</v>
+        <v>0.7063182895288347</v>
       </c>
       <c r="W23" t="n">
-        <v>50</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1025201612903226</v>
+        <v>-0.1476853287841191</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.2958350134408603</v>
+        <v>0.2754908498759305</v>
       </c>
       <c r="Z23" t="n">
-        <v>-0.9190264624361857</v>
+        <v>-0.9590709350779295</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.36135651152005</v>
+        <v>1.21235822390285</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.802</v>
+        <v>0.635</v>
       </c>
       <c r="AC23" t="b">
         <v>1</v>
@@ -2752,11 +2796,11 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>有效(方向相反)</t>
+          <t>边际可用</t>
         </is>
       </c>
       <c r="AF23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2766,89 +2810,89 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>10</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.09403225806451614</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.1826830772609757</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.5147288926504365</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.906656342498581</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.08893617777895146</v>
+      </c>
+      <c r="H24" t="n">
+        <v>70</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.0105241935483871</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.1775806451612903</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.05948351707211004</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.218151620482692</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="N24" t="b">
+        <v>0</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>拥挤=风险(期望负)</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>优秀(方向相反)</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
         <v>9</v>
       </c>
-      <c r="C24" t="n">
-        <v>0.09077060931899643</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.1934555855775858</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.4692064540188356</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1.668013948630808</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.1338683848386175</v>
-      </c>
-      <c r="H24" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="I24" t="n">
-        <v>-0.003014112903225791</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.19081541218638</v>
-      </c>
-      <c r="K24" t="n">
-        <v>-0.01523817606501985</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.249126652362237</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0.969</v>
-      </c>
-      <c r="N24" t="b">
-        <v>1</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>拥挤=风险(期望负)</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>有效(方向相反)</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>8</v>
-      </c>
       <c r="R24" t="n">
-        <v>-0.01607862903225806</v>
+        <v>-0.0482078853046595</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1070682890042348</v>
+        <v>0.1390009646515677</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1501717192064415</v>
+        <v>-0.3468169118502287</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6448926891150488</v>
+        <v>-1.225766679591739</v>
       </c>
       <c r="V24" t="n">
-        <v>0.5395487986655532</v>
+        <v>0.2551436788265742</v>
       </c>
       <c r="W24" t="n">
-        <v>62.5</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.05171370967741935</v>
+        <v>-0.1173835125448029</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.01955645161290323</v>
+        <v>0.02011648745519714</v>
       </c>
       <c r="Z24" t="n">
-        <v>-0.413825499559353</v>
+        <v>-0.7619427653469889</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.2945419996668496</v>
+        <v>0.3155811459505954</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.229</v>
+        <v>0.09</v>
       </c>
       <c r="AC24" t="b">
         <v>1</v>
@@ -2860,7 +2904,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>无效</t>
+          <t>有效</t>
         </is>
       </c>
       <c r="AF24" t="b">
@@ -2874,40 +2918,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C25" t="n">
-        <v>0.08790322580645163</v>
+        <v>0.1179435483870968</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2347005413451369</v>
+        <v>0.2408071245552323</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3745335451833759</v>
+        <v>0.4897842977234874</v>
       </c>
       <c r="F25" t="n">
-        <v>1.839743524602421</v>
+        <v>2.373746156193504</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1030859152172374</v>
+        <v>0.04165245246650207</v>
       </c>
       <c r="H25" t="n">
-        <v>66.66666666666666</v>
+        <v>70</v>
       </c>
       <c r="I25" t="n">
-        <v>0.01115927419354839</v>
+        <v>0.05379032258064518</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1785315860215052</v>
+        <v>0.1831048387096774</v>
       </c>
       <c r="K25" t="n">
-        <v>0.06201558704421735</v>
+        <v>0.2469550162776364</v>
       </c>
       <c r="L25" t="n">
-        <v>0.7729549410943776</v>
+        <v>0.8957819686219202</v>
       </c>
       <c r="M25" t="n">
-        <v>0.985</v>
+        <v>1</v>
       </c>
       <c r="N25" t="b">
         <v>0</v>
@@ -2923,40 +2967,40 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R25" t="n">
-        <v>-0.0282258064516129</v>
+        <v>-0.03082437275985663</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1881164609594299</v>
+        <v>0.1761394346679306</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1500443199263685</v>
+        <v>-0.1749998392919151</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5653104062780686</v>
+        <v>-0.6794798939692601</v>
       </c>
       <c r="V25" t="n">
-        <v>0.5895137299923587</v>
+        <v>0.5160083327375322</v>
       </c>
       <c r="W25" t="n">
-        <v>25</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.1328629032258065</v>
+        <v>-0.1253136200716846</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.07641129032258065</v>
+        <v>0.06161850358422938</v>
       </c>
       <c r="Z25" t="n">
-        <v>-1.096877020629011</v>
+        <v>-1.163306451257045</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.4334460468545435</v>
+        <v>0.3661614819764399</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.296</v>
+        <v>0.27</v>
       </c>
       <c r="AC25" t="b">
         <v>1</v>
@@ -2968,7 +3012,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>无效</t>
+          <t>边际可用</t>
         </is>
       </c>
       <c r="AF25" t="b">
@@ -2982,13 +3026,17 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1370967741935484</v>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+        <v>0.1977822580645162</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.08582223432949627</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.304557316757486</v>
+      </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
@@ -3007,18 +3055,22 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>边际可用</t>
+          <t>优秀</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>-0.1423387096774194</v>
+      </c>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
@@ -3032,7 +3084,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>样本不足</t>
+          <t>边际可用</t>
         </is>
       </c>
       <c r="AF26" t="b">
@@ -3046,37 +3098,37 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1357862903225807</v>
+        <v>0.1384408602150538</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1569536149604247</v>
+        <v>0.1470324905074668</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8651364312750536</v>
+        <v>0.9415664506344148</v>
       </c>
       <c r="F27" t="n">
-        <v>2.807633949763004</v>
+        <v>3.216715505130622</v>
       </c>
       <c r="G27" t="n">
-        <v>0.02623492509365355</v>
+        <v>0.01229967063463677</v>
       </c>
       <c r="H27" t="n">
-        <v>87.5</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="I27" t="n">
-        <v>0.07026209677419355</v>
+        <v>0.0710573476702509</v>
       </c>
       <c r="J27" t="n">
-        <v>0.2013104838709678</v>
+        <v>0.2117831541218638</v>
       </c>
       <c r="K27" t="n">
-        <v>0.4914179151580647</v>
+        <v>0.4832637016929802</v>
       </c>
       <c r="L27" t="n">
-        <v>1.766362309495952</v>
+        <v>1.858389628426363</v>
       </c>
       <c r="M27" t="n">
         <v>1</v>
@@ -3095,43 +3147,43 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.05576036866359448</v>
+        <v>-0.06154233870967743</v>
       </c>
       <c r="S27" t="n">
-        <v>0.1127343000585549</v>
+        <v>0.1056451475489842</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.4946175976134344</v>
+        <v>-0.5825382437100789</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.282465168721678</v>
+        <v>-1.736529262856342</v>
       </c>
       <c r="V27" t="n">
-        <v>0.2469952304759364</v>
+        <v>0.1260449864239404</v>
       </c>
       <c r="W27" t="n">
-        <v>28.57142857142857</v>
+        <v>25</v>
       </c>
       <c r="X27" t="n">
-        <v>-0.1258640552995392</v>
+        <v>-0.1209173387096774</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.01434331797235023</v>
+        <v>-0.002167338709677422</v>
       </c>
       <c r="Z27" t="n">
-        <v>-2.643538176664004</v>
+        <v>-1.823568434216566</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.1614800027538029</v>
+        <v>-0.02303013242113114</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.099</v>
+        <v>0.02</v>
       </c>
       <c r="AC27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -3140,7 +3192,7 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>有效(方向相反)</t>
+          <t>优秀(方向相反)</t>
         </is>
       </c>
       <c r="AF27" t="b">
@@ -3154,14 +3206,18 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.3479838709677419</v>
+      </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>100</v>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
@@ -3175,7 +3231,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>样本不足</t>
+          <t>边际可用</t>
         </is>
       </c>
       <c r="Q28" t="n">
@@ -19092,56 +19148,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>持有时长</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>触发次数</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>均值</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>中位数</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>负收益概率</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>t值</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>p值</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>无条件均值</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>无条件负概率</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>是否满足有效标准</t>
         </is>
@@ -19154,30 +19210,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2081322609472731</v>
+        <v>0.9534000088940247</v>
       </c>
       <c r="D2" t="n">
         <v>-9.551429848078646</v>
       </c>
       <c r="E2" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02437229481703635</v>
+        <v>0.1212900891498364</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9812358727447867</v>
+        <v>0.90612610851549</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.06180763944742505</v>
+        <v>0.2407233596708958</v>
       </c>
       <c r="I2" t="n">
-        <v>53.70018975332068</v>
+        <v>52.8110599078341</v>
       </c>
       <c r="J2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>6个月(=2季度)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-5.41737001096056</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-5.81225166797657</v>
+      </c>
+      <c r="E3" t="n">
+        <v>75</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-1.169819474454885</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.2803576607067929</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.1003113922029837</v>
+      </c>
+      <c r="I3" t="n">
+        <v>54.7438330170778</v>
+      </c>
+      <c r="J3" t="b">
         <v>0</v>
       </c>
     </row>
